--- a/howTo/MCU/risc-v/RISCV_RefCard.xlsx
+++ b/howTo/MCU/risc-v/RISCV_RefCard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wl\tool_portable\msys64\home\wl.hsu\working\private\my_code\my_note\howTo\MCU\risc-v\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B604529F-9DC8-457E-A86C-094E9CEB2EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F5D68A-5DB9-4C8F-9CAA-D1CB376CC1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9240" yWindow="795" windowWidth="27780" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12000" yWindow="285" windowWidth="27780" windowHeight="14655" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GPRs" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="576">
   <si>
     <t xml:space="preserve">Inst   </t>
   </si>
@@ -419,15 +419,6 @@
     <t>rd = rs1 % rs2</t>
   </si>
   <si>
-    <t xml:space="preserve">la rd, symbol               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">l{b|h|w|d} rd, symbol       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">s{b|h|w|d} rd, symbol, rt   </t>
-  </si>
-  <si>
     <t xml:space="preserve">fl{w|d} rd, symbol, rt      </t>
   </si>
   <si>
@@ -437,9 +428,6 @@
     <t xml:space="preserve">nop                         </t>
   </si>
   <si>
-    <t xml:space="preserve">li rd, immediate            </t>
-  </si>
-  <si>
     <t xml:space="preserve">mv rd, rs                   </t>
   </si>
   <si>
@@ -449,15 +437,6 @@
     <t xml:space="preserve">neg rd, rs                  </t>
   </si>
   <si>
-    <t xml:space="preserve">negw rd, rs                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sext.w rd, rs               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">seqz rd, rs                 </t>
-  </si>
-  <si>
     <t xml:space="preserve">snez rd, rs                 </t>
   </si>
   <si>
@@ -467,9 +446,6 @@
     <t xml:space="preserve">sgtz rd, rs                 </t>
   </si>
   <si>
-    <t xml:space="preserve">fmv.s rd, rs                </t>
-  </si>
-  <si>
     <t xml:space="preserve">fabs.s rd, rs               </t>
   </si>
   <si>
@@ -485,9 +461,6 @@
     <t xml:space="preserve">fneg.d rd, rs               </t>
   </si>
   <si>
-    <t xml:space="preserve">beqz rs, offset             </t>
-  </si>
-  <si>
     <t xml:space="preserve">bnez rs, offset             </t>
   </si>
   <si>
@@ -530,9 +503,6 @@
     <t xml:space="preserve">ret </t>
   </si>
   <si>
-    <t xml:space="preserve">call offset </t>
-  </si>
-  <si>
     <t xml:space="preserve">tail offset </t>
   </si>
   <si>
@@ -638,21 +608,9 @@
     <t xml:space="preserve">jalr x0, x1, 0 </t>
   </si>
   <si>
-    <t xml:space="preserve">fence iorw, iorw </t>
-  </si>
-  <si>
     <t>Meaning</t>
   </si>
   <si>
-    <t>Load address</t>
-  </si>
-  <si>
-    <t>Load global</t>
-  </si>
-  <si>
-    <t>Store global</t>
-  </si>
-  <si>
     <t>Floating-point load global</t>
   </si>
   <si>
@@ -662,202 +620,10 @@
     <t>No operation</t>
   </si>
   <si>
-    <t>Load immediate</t>
-  </si>
-  <si>
-    <t>Copy register</t>
-  </si>
-  <si>
-    <t>One's complement</t>
-  </si>
-  <si>
-    <t>Two's complement</t>
-  </si>
-  <si>
-    <t>Two's complement word</t>
-  </si>
-  <si>
-    <t>Sign extend word</t>
-  </si>
-  <si>
-    <t>Set if = zero</t>
-  </si>
-  <si>
-    <t>Set if ̸= zero</t>
-  </si>
-  <si>
-    <t>Set if &lt; zero</t>
-  </si>
-  <si>
-    <t>Set if &gt; zero</t>
-  </si>
-  <si>
-    <t>Copy single-precision register</t>
-  </si>
-  <si>
-    <t>Single-precision absolute value</t>
-  </si>
-  <si>
-    <t>Single-precision negate</t>
-  </si>
-  <si>
-    <t>Copy double-precision register</t>
-  </si>
-  <si>
-    <t>Double-precision absolute value</t>
-  </si>
-  <si>
-    <t>Double-precision negate</t>
-  </si>
-  <si>
-    <t>Branch if = zero</t>
-  </si>
-  <si>
-    <t>Branch if ̸= zero</t>
-  </si>
-  <si>
-    <t>Branch if &lt; zero</t>
-  </si>
-  <si>
-    <t>Branch if &gt; zero</t>
-  </si>
-  <si>
-    <t>Branch if &gt;</t>
-  </si>
-  <si>
-    <t>Branch if &gt;, unsigned</t>
-  </si>
-  <si>
-    <t>Jump</t>
-  </si>
-  <si>
-    <t>Jump and link</t>
-  </si>
-  <si>
-    <t>Jump register</t>
-  </si>
-  <si>
-    <t>Jump and link register</t>
-  </si>
-  <si>
-    <t>Return from subroutine</t>
-  </si>
-  <si>
     <t>Call far-away subroutine</t>
   </si>
   <si>
-    <t>Tail call far-away subroutine</t>
-  </si>
-  <si>
     <t>Fence on all memory and I/O</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Branch if </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>≤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> zero</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Branch if </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> zero</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Branch if </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>≤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Branch if </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-      </rPr>
-      <t>≤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, unsigned</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">auipc rd, symbol[31:12]       
-addi rd, rd, symbol[11:0]  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">auipc rd, symbol[31:12]   
-l{b|h|w|d} rd, symbol[11:0](rd)      </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">auipc rt, symbol[31:12]    
-s{b|h|w|d} rd, symbol[11:0](rt)     </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">auipc rt, symbol[31:12]   
-fl{w|d} rd, symbol[11:0](rt)      </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">auipc rt, symbol[31:12]      
-fs{w|d} rd, symbol[11:0](rt)   </t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Inst      </t>
@@ -1763,10 +1529,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>jalr rd, rs1, simm12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rd = PC+4; PC += simm21
 ps. 'rd'  will be 'x1' register</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1825,16 +1587,6 @@
   <si>
     <t>U-Mode return</t>
     <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>auipc x1, offset[31:12] 
-jalr x1, x1, offset[11:0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>auipc x6, offset[31:12] 
-jalr x0, x6, offset[11:0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Transfer control to OS system call
@@ -2174,10 +1926,6 @@
     <t>x1</t>
   </si>
   <si>
-    <t>ra</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Return Address</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2338,6 +2086,1307 @@
   </si>
   <si>
     <t>ps. Standard RV32E(for MCU) only support  x0 ~ x15 and PC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">la t0, trap_entry
+lla t2, _load_start </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mv  tp, a0
+mv  gp, zero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jal uart_init</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">la t5, board_init_f
+jalr t5 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Load (Local) Address
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = &amp;symbol</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Load global
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = *((xxx*)(rs1 + simm))</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store global
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+*((xxx*)(rs1 + simm)) = rd </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>not x5, x6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neg x5, x6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Copy register
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = rs</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">li rd, immediate            </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Load immediate
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = immediate </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set if = zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = (rs == 0) ? 1 : 0</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set if ̸= zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = (rs != 0) ? 1 : 0</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set if &gt; zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = (rs &gt; 0) ? 1 : 0</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set if &lt; zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = (rs &lt; 0) ? 1 : 0</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>la rd, symbol 
+lla rd, symbol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sign extend word
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = sext(rs[31: 0])</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">One's complement
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = ~rs</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two's complement
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rd = -1 * rs</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two's complement word
+C-Code:
+rd = -1 * rs[31: 0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">seqz rd, rs                 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">beqz rs, offset             </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beqz a0, board_init</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if = zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+if( rs == 0 ) goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if ̸= zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">C-Code:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>if( rs != 0 ) goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if &lt;= zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+if( rs &lt;= 0 ) goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if &gt;= zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+if( rs &gt;= 0 ) goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if &lt; zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+if( rs &lt; 0 ) goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if &gt; zero
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+if( rs &gt; 0 ) goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if rs &gt; rt
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+if( rs &gt; rt ) goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">rs &lt;= rt
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+if( rs &lt;= rt ) goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if (usig)rs &gt; (usig)rt 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+if( (unsigned)rs &gt; (unsigned)rt ) 
+    goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branch if (usig)rs &lt;= (usig)rt 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+if( (unsigned)rs &lt;= (unsigned)rt ) 
+    goto offset</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jump
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+pc += rs</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ble t1, t2, 6b
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Backward(context up) label '6'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">j 10f
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Forward(context down) label '10'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">negw rd, rs
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+RV64I only</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">sext.w rd, rs
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>note:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+RV64I only</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jump and link
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">C-Code:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x1= pc + 4;
+pc += rs;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jump register
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+pc = rs</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jalr rd, rs1, simm12
+jalr rd, simm12(rs1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">la t5, board_init_f
+jr t5 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jump and link register
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+x1= pc + 4;
+pc = rs;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Return from subroutine
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+return</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auipc rt, symbol[31:12]
+fl{w|d} rd, symbol[11:0](rt)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auipc rt, symbol[31:12]
+fs{w|d} rd, symbol[11:0](rt)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step1. auipc x1, offset[31:12] 
+step2. jalr x1, x1, offset[11:0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step1. auipc x6, offset[31:12] 
+step2. jalr x0, x6, offset[11:0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">fmv.s rd, rs                </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra (lr)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">call offset </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>call rd, symbol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step1. auipc rd, offset[31:12] 
+step2. jalr x1, rd, offset[11:0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Call away subroutine
+ps. similar 'call' but use '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>' to replace '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Tail call far-away subroutine
+ps. similar 'call' but use '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>' to replace '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Copy single-precision register
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(float)rd = (float)rs;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Copy double-precision register
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(double)rd = (double)rs;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Single-precision absolute value
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(float)rd = (float)fabs(rs);</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Double-precision absolute value
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(double)rd = (double)fabs(rs);</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Single-precision negate
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(float)rd = -1 * (float)rs;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Double-precision negate
+C-Code:
+(double)rd = -1 * (double)rs;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fence pred, succ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fence iorw, iorw
+fence  rw, rw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">l{b|h|w|d} rd, symbol 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+ld =&gt; Load DWord (RV64I only) </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">s{b|h|w|d} rd, symbol, rt 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+sd =&gt; Store DWord (RV64I only)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">step1. auipc rd, symbol[31:12] 
+step2. addi rd, rd, symbol[11:0] </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step1. auipc rd, symbol[31:12]
+step2. l{b|h|w|d} rd, symbol[11:0](rd)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">step1. auipc rt, symbol[31:12]
+step2. s{b|h|w|d} rd, symbol[11:0](rt) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(?) sw t1, _load_start
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(?) ld t5, trap_entry</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2345,7 +3394,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2411,6 +3460,26 @@
     <font>
       <sz val="14"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2560,11 +3629,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2572,6 +3641,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2857,233 +3931,233 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>510</v>
+        <v>456</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>511</v>
+        <v>457</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>512</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>513</v>
+        <v>459</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>514</v>
+        <v>460</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>515</v>
+        <v>461</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>516</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>519</v>
+        <v>464</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>521</v>
+        <v>466</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>522</v>
+        <v>467</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>523</v>
+        <v>468</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>524</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>525</v>
+        <v>470</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>526</v>
+        <v>471</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>527</v>
+        <v>472</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>516</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>528</v>
+        <v>473</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>529</v>
+        <v>474</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>531</v>
+        <v>476</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>532</v>
+        <v>477</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>533</v>
+        <v>478</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>534</v>
+        <v>479</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>535</v>
+        <v>480</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>536</v>
+        <v>481</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="54" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>537</v>
+        <v>482</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>538</v>
+        <v>483</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>539</v>
+        <v>484</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>524</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>540</v>
+        <v>485</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>541</v>
+        <v>486</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>542</v>
+        <v>487</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>543</v>
+        <v>488</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>544</v>
+        <v>489</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>545</v>
+        <v>490</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>554</v>
+        <v>499</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>555</v>
+        <v>500</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>546</v>
+        <v>491</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>556</v>
+        <v>501</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>557</v>
+        <v>502</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>546</v>
+        <v>491</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>547</v>
+        <v>492</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>548</v>
+        <v>493</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>549</v>
+        <v>494</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>524</v>
+        <v>469</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>550</v>
+        <v>495</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>551</v>
+        <v>496</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>536</v>
+        <v>481</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>552</v>
+        <v>497</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>552</v>
+        <v>497</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>553</v>
+        <v>498</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
-        <v>559</v>
-      </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
+      <c r="A17" s="26" t="s">
+        <v>504</v>
+      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3132,7 +4206,7 @@
         <v>76</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3146,7 +4220,7 @@
         <v>77</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3160,7 +4234,7 @@
         <v>78</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>407</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3174,7 +4248,7 @@
         <v>79</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>408</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3188,7 +4262,7 @@
         <v>80</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>409</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3202,7 +4276,7 @@
         <v>81</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>410</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3216,7 +4290,7 @@
         <v>82</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>411</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3230,7 +4304,7 @@
         <v>83</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>412</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3244,7 +4318,7 @@
         <v>84</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>413</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3258,7 +4332,7 @@
         <v>85</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>414</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3269,10 +4343,10 @@
         <v>48</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>415</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3283,10 +4357,10 @@
         <v>49</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>422</v>
+        <v>371</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3297,10 +4371,10 @@
         <v>50</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>421</v>
+        <v>370</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>417</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3311,10 +4385,10 @@
         <v>51</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>418</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3328,7 +4402,7 @@
         <v>86</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>419</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3342,7 +4416,7 @@
         <v>87</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3356,7 +4430,7 @@
         <v>88</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3367,10 +4441,10 @@
         <v>55</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>426</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="18" x14ac:dyDescent="0.25">
@@ -3381,10 +4455,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>428</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
@@ -3395,10 +4469,10 @@
         <v>57</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>430</v>
+        <v>379</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
@@ -3409,10 +4483,10 @@
         <v>58</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
@@ -3423,10 +4497,10 @@
         <v>59</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>433</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
@@ -3437,10 +4511,10 @@
         <v>60</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
@@ -3451,10 +4525,10 @@
         <v>61</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>436</v>
+        <v>385</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
@@ -3465,10 +4539,10 @@
         <v>62</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>435</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
@@ -3479,10 +4553,10 @@
         <v>63</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
@@ -3493,10 +4567,10 @@
         <v>64</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3507,10 +4581,10 @@
         <v>65</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>493</v>
+        <v>439</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3521,10 +4595,10 @@
         <v>66</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>494</v>
+        <v>440</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3535,10 +4609,10 @@
         <v>67</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>495</v>
+        <v>441</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3549,38 +4623,38 @@
         <v>90</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>496</v>
+        <v>442</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="36" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>497</v>
+        <v>443</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="36" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>91</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>498</v>
+        <v>444</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>452</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3591,10 +4665,10 @@
         <v>69</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>456</v>
+        <v>404</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>454</v>
+        <v>403</v>
       </c>
     </row>
     <row r="36" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3605,10 +4679,10 @@
         <v>70</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>455</v>
+        <v>405</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3619,10 +4693,10 @@
         <v>71</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>458</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3633,10 +4707,10 @@
         <v>72</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>461</v>
+        <v>409</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>459</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="36" x14ac:dyDescent="0.25">
@@ -3647,7 +4721,7 @@
         <v>73</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>472</v>
+        <v>418</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>36</v>
@@ -3655,144 +4729,144 @@
     </row>
     <row r="40" spans="2:5" ht="36" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
-        <v>462</v>
+        <v>410</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>74</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>473</v>
+        <v>419</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>463</v>
+        <v>411</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="18" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
-        <v>464</v>
+        <v>412</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>465</v>
+        <v>413</v>
       </c>
       <c r="D41" s="11"/>
       <c r="E41" s="9" t="s">
-        <v>464</v>
+        <v>412</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="18" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
-        <v>466</v>
+        <v>414</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>467</v>
+        <v>415</v>
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="9" t="s">
-        <v>466</v>
+        <v>414</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="18" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>469</v>
+        <v>417</v>
       </c>
       <c r="D43" s="11"/>
       <c r="E43" s="9" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B44" s="26" t="s">
-        <v>474</v>
-      </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
+      <c r="B44" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
     </row>
     <row r="45" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>487</v>
+        <v>433</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>476</v>
+        <v>422</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>499</v>
+        <v>445</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="90.75" x14ac:dyDescent="0.25">
       <c r="B46" s="5" t="s">
-        <v>481</v>
+        <v>427</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>488</v>
+        <v>434</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>482</v>
+        <v>428</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>503</v>
+        <v>449</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="72.75" x14ac:dyDescent="0.25">
       <c r="B47" s="12" t="s">
-        <v>477</v>
+        <v>423</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>489</v>
+        <v>435</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>478</v>
+        <v>424</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>500</v>
+        <v>446</v>
       </c>
     </row>
     <row r="48" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
       <c r="B48" s="5" t="s">
-        <v>483</v>
+        <v>429</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>490</v>
+        <v>436</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>484</v>
+        <v>430</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>502</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="72.75" x14ac:dyDescent="0.25">
       <c r="B49" s="12" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>491</v>
+        <v>437</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>480</v>
+        <v>426</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>501</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
       <c r="B50" s="5" t="s">
-        <v>485</v>
+        <v>431</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>492</v>
+        <v>438</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>486</v>
+        <v>432</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>504</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -3807,520 +4881,558 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C0B9B54-3CA8-465F-9D50-8A576FE04F33}">
-  <dimension ref="B1:E41"/>
+  <dimension ref="B1:E42"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="35.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="46.140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="41.42578125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" style="4" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="18" x14ac:dyDescent="0.25">
       <c r="B1" s="25" t="s">
-        <v>558</v>
+        <v>503</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E1" s="25" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="2:5" ht="36" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>115</v>
+    <row r="2" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>521</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="2:5" ht="36" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
-        <v>116</v>
+        <v>571</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>569</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="2:5" ht="36" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>117</v>
+        <v>572</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E4" s="5"/>
+        <v>573</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>574</v>
+      </c>
     </row>
     <row r="5" spans="2:5" ht="36" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>233</v>
+        <v>550</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="2:5" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>234</v>
+        <v>551</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="2:5" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="D17" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="D18" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D19" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="D20" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D21" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="D22" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="2:5" ht="54" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D23" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D24" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D25" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="D26" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="D27" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="D28" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="D29" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D30" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31" spans="2:5" ht="72.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="D31" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="72.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="D32" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" spans="2:5" ht="72.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="D33" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="2:5" ht="72.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="D34" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="72.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="D35" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="D36" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="72.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B28" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="D37" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="54.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B32" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E35" s="5"/>
-    </row>
-    <row r="36" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B36" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E36" s="5"/>
-    </row>
-    <row r="37" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B38" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>222</v>
+      <c r="D38" s="6" t="s">
+        <v>549</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>507</v>
+        <v>453</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="36" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
-        <v>152</v>
+        <v>556</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>470</v>
+        <v>552</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="36" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="54" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
-        <v>153</v>
+        <v>557</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" ht="18" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="2:5" ht="54" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E41" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="36" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>568</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4469,13 +5581,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>89</v>
@@ -4483,325 +5595,325 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>280</v>
+        <v>229</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>265</v>
+        <v>214</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>244</v>
+        <v>193</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>285</v>
+        <v>234</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>287</v>
+        <v>236</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>288</v>
+        <v>237</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>289</v>
+        <v>238</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>249</v>
+        <v>198</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>270</v>
+        <v>219</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>250</v>
+        <v>199</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>292</v>
+        <v>241</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>252</v>
+        <v>201</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>273</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>256</v>
+        <v>205</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>298</v>
+        <v>247</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>262</v>
+        <v>211</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>275</v>
+        <v>224</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>303</v>
+        <v>252</v>
       </c>
       <c r="D28" s="2"/>
     </row>
@@ -4825,7 +5937,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>101</v>
@@ -4839,109 +5951,109 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>313</v>
+        <v>262</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>305</v>
+        <v>254</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>314</v>
+        <v>263</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>315</v>
+        <v>264</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>307</v>
+        <v>256</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>316</v>
+        <v>265</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>324</v>
+        <v>273</v>
       </c>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>308</v>
+        <v>257</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>325</v>
+        <v>274</v>
       </c>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>309</v>
+        <v>258</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>310</v>
+        <v>259</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
       <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>311</v>
+        <v>260</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>312</v>
+        <v>261</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="D10" s="5"/>
     </row>
@@ -4964,10 +6076,10 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>110</v>
@@ -4978,82 +6090,82 @@
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>358</v>
+        <v>307</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>383</v>
+        <v>332</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>384</v>
+        <v>333</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>360</v>
+        <v>309</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>334</v>
+        <v>283</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>361</v>
+        <v>310</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>335</v>
+        <v>284</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>387</v>
+        <v>336</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>363</v>
+        <v>312</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>364</v>
+        <v>313</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>76</v>
@@ -5062,10 +6174,10 @@
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>338</v>
+        <v>287</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>77</v>
@@ -5074,22 +6186,22 @@
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>389</v>
+        <v>338</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>340</v>
+        <v>289</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>113</v>
@@ -5098,193 +6210,193 @@
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>341</v>
+        <v>290</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>369</v>
+        <v>318</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>391</v>
+        <v>340</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>343</v>
+        <v>292</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>370</v>
+        <v>319</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>371</v>
+        <v>320</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>393</v>
+        <v>342</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>372</v>
+        <v>321</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>373</v>
+        <v>322</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>395</v>
+        <v>344</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>374</v>
+        <v>323</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>396</v>
+        <v>345</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>396</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>398</v>
+        <v>347</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>377</v>
+        <v>326</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>399</v>
+        <v>348</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>352</v>
+        <v>301</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>400</v>
+        <v>349</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>401</v>
+        <v>350</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>402</v>
+        <v>351</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>381</v>
+        <v>330</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>356</v>
+        <v>305</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>382</v>
+        <v>331</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="D27" s="2"/>
     </row>
